--- a/demo-data/Sample_Deal_Requests.xlsx
+++ b/demo-data/Sample_Deal_Requests.xlsx
@@ -7,14 +7,21 @@
     <sheet name="Line Items" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Deal Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Line Items'!$A$4:$O$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Deal Summary'!$A$4:$Q$14</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -36,8 +43,12 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +70,13 @@
         <fgColor rgb="FF0F766E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border/>
     <border>
       <left style="thin">
@@ -76,11 +92,25 @@
         <color rgb="FFC9D3DD"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9E2F3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9E2F3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2F3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +136,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -403,8 +454,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:U14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12.25" customWidth="1" min="1" max="1"/>
     <col width="15.63000011444092" customWidth="1" min="2" max="2"/>
@@ -453,82 +504,97 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Customer ID</t>
+          <t>Sold-To Customer ID</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Customer Name</t>
+          <t>Sold-To Customer Name</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>Opportunity ID</t>
+          <t>End Account ID</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
+          <t>End Account Name</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
           <t>Deal Type</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>Customer Type</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>Customer Type</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>Sales Owner</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>Sales Manager</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="L4" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
-        <is>
-          <t>Target Close Date</t>
-        </is>
-      </c>
       <c r="M4" s="11" t="inlineStr">
         <is>
+          <t>Expected Award / Decision Date</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>Requested Delivery Start</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>Requested Delivery End</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr">
+        <is>
           <t>Payment Terms</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
-        <is>
-          <t>Contract Months</t>
-        </is>
-      </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="Q4" s="11" t="inlineStr">
         <is>
           <t>Strategic Rationale</t>
         </is>
       </c>
-      <c r="P4" s="11" t="inlineStr">
-        <is>
-          <t>Intake Risk</t>
-        </is>
-      </c>
-      <c r="Q4" s="11" t="inlineStr">
+      <c r="R4" s="11" t="inlineStr">
+        <is>
+          <t>KAM Risk Assessment</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Risk Reason</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="R4" s="11" t="inlineStr">
-        <is>
-          <t>Included_In_Latest_Financial_Plan</t>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Included In Latest Financial Plan</t>
         </is>
       </c>
     </row>
@@ -540,83 +606,100 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Northstar Oncology Infusion Expansion</t>
+          <t>Region A Infusion Tender Defense</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
+          <t>CUST-1004</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>HelioRx Distribution</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
           <t>CUST-1001</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Northstar Health Systems</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>OPP-4001</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>Competitive replacement</t>
-        </is>
-      </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>Enterprise Account</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
+          <t>Region A</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
           <t>Maya Chen</t>
         </is>
       </c>
-      <c r="J5" s="13" t="inlineStr">
+      <c r="K5" s="13" t="inlineStr">
         <is>
           <t>Jordan Blake</t>
         </is>
       </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="L5" s="13" t="inlineStr">
+      <c r="M5" s="13" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="M5" s="13" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="O5" s="13" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="P5" s="13" t="inlineStr">
         <is>
           <t>Net 60</t>
         </is>
       </c>
-      <c r="N5" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="O5" s="13" t="inlineStr">
-        <is>
-          <t>Competitor incumbent pressure; oncology infusion standardization.</t>
-        </is>
-      </c>
-      <c r="P5" s="13" t="inlineStr">
+      <c r="Q5" s="13" t="inlineStr">
+        <is>
+          <t>Tender defense against aggressive competitor pricing; requested discount protects annual volume while staying within product guidance.</t>
+        </is>
+      </c>
+      <c r="R5" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="Q5" s="13" t="inlineStr">
-        <is>
-          <t>Enterprise Account</t>
-        </is>
-      </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Competitor price pressure</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Distributor</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -630,7 +713,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Meridian Biosimilar Conversion</t>
+          <t>Retail Chain Conversion Program</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -645,68 +728,85 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>OPP-4002</t>
+          <t>CUST-1002</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Expansion</t>
+          <t>Meridian Specialty Pharmacy</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>New Account / Launch</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Specialty Distributor</t>
+          <t>Retail / Pharmacy Chain</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
+          <t>Region A</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
           <t>Ethan Brooks</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>Lena Torres</t>
-        </is>
-      </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
+          <t>Jordan Blake</t>
+        </is>
+      </c>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="L6" s="13" t="inlineStr">
+      <c r="M6" s="13" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="M6" s="13" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="O6" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="P6" s="13" t="inlineStr">
         <is>
           <t>Net 45</t>
         </is>
       </c>
-      <c r="N6" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="O6" s="13" t="inlineStr">
-        <is>
-          <t>Biosimilar conversion with specialty pharmacy volume commitment.</t>
-        </is>
-      </c>
-      <c r="P6" s="13" t="inlineStr">
+      <c r="Q6" s="13" t="inlineStr">
+        <is>
+          <t>Strategic launch support for a retail pharmacy chain; short-term discount expected to secure listing and unlock repeat demand.</t>
+        </is>
+      </c>
+      <c r="R6" s="13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q6" s="13" t="inlineStr">
-        <is>
-          <t>Specialty Distributor</t>
-        </is>
-      </c>
-      <c r="R6" s="13" t="inlineStr">
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>New account acquisition</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Retail / Pharmacy Chain</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -720,7 +820,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Apex National Formulary Access</t>
+          <t>National Buying Group Renewal</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
@@ -735,17 +835,17 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>OPP-4003</t>
+          <t>CUST-1003</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Strategic exception</t>
+          <t>Apex National GPO</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Contract Renewal</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
@@ -755,48 +855,65 @@
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
+          <t>Region A</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
           <t>Maya Chen</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="K7" s="13" t="inlineStr">
         <is>
           <t>Jordan Blake</t>
         </is>
       </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="L7" s="13" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="L7" s="13" t="inlineStr">
+      <c r="M7" s="13" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M7" s="13" t="inlineStr">
+      <c r="N7" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="O7" s="13" t="inlineStr">
+        <is>
+          <t>2027-03-31</t>
+        </is>
+      </c>
+      <c r="P7" s="13" t="inlineStr">
         <is>
           <t>Net 90</t>
         </is>
       </c>
-      <c r="N7" s="13" t="n">
-        <v>48</v>
-      </c>
-      <c r="O7" s="13" t="inlineStr">
-        <is>
-          <t>National GPO preferred formulary position with rebate pressure.</t>
-        </is>
-      </c>
-      <c r="P7" s="13" t="inlineStr">
+      <c r="Q7" s="13" t="inlineStr">
+        <is>
+          <t>Contract renewal needed to defend incumbent position after competitor entry; proposal balances access retention with product margin guardrails.</t>
+        </is>
+      </c>
+      <c r="R7" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="Q7" s="13" t="inlineStr">
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Incumbent defense</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>Buying Group</t>
         </is>
       </c>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -810,7 +927,7 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>HelioRx Rare Disease EU Launch</t>
+          <t>Region B Launch Stocking Offer</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -825,17 +942,17 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>OPP-4004</t>
+          <t>CUST-1007</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>New Sale</t>
+          <t>Orion Hospital Trust</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>New Account / Launch</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
@@ -845,48 +962,65 @@
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
+          <t>Region B</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
           <t>Sofia Romano</t>
         </is>
       </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="K8" s="13" t="inlineStr">
         <is>
           <t>Jordan Blake</t>
         </is>
       </c>
-      <c r="K8" s="13" t="inlineStr">
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="M8" s="13" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="M8" s="13" t="inlineStr">
+      <c r="N8" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="O8" s="13" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="P8" s="13" t="inlineStr">
         <is>
           <t>Net 60</t>
         </is>
       </c>
-      <c r="N8" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="O8" s="13" t="inlineStr">
-        <is>
-          <t>EU5 rare disease launch with cold-chain allocation risk.</t>
-        </is>
-      </c>
-      <c r="P8" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
       <c r="Q8" s="13" t="inlineStr">
         <is>
+          <t>Strategic launch support for new institutional demand; introductory price expected to secure preferred stocking and repeat orders.</t>
+        </is>
+      </c>
+      <c r="R8" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>New account acquisition</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>Distributor</t>
         </is>
       </c>
-      <c r="R8" s="13" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -900,7 +1034,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Summit Oncology Biosimilar Pilot</t>
+          <t>Institution Pilot Access Package</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -915,68 +1049,85 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>OPP-4005</t>
+          <t>CUST-1005</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>New Sale</t>
+          <t>Summit Oncology Clinics</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>New Account / Launch</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>Provider Network</t>
+          <t>Hospital / Institution</t>
         </is>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
+          <t>Region A</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
           <t>Noah Patel</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>Lena Torres</t>
-        </is>
-      </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
+          <t>Jordan Blake</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="L9" s="13" t="inlineStr">
+      <c r="M9" s="13" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="M9" s="13" t="inlineStr">
+      <c r="N9" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="P9" s="13" t="inlineStr">
         <is>
           <t>Net 30</t>
         </is>
       </c>
-      <c r="N9" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="O9" s="13" t="inlineStr">
-        <is>
-          <t>Community oncology biosimilar pilot with diagnostics attach.</t>
-        </is>
-      </c>
-      <c r="P9" s="13" t="inlineStr">
+      <c r="Q9" s="13" t="inlineStr">
+        <is>
+          <t>Pilot access package for a regional institution; pricing remains within target margin and supports future standard-volume conversion.</t>
+        </is>
+      </c>
+      <c r="R9" s="13" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="Q9" s="13" t="inlineStr">
-        <is>
-          <t>Provider Network</t>
-        </is>
-      </c>
-      <c r="R9" s="13" t="inlineStr">
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>New account acquisition</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Hospital / Institution</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -990,7 +1141,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>Cityline Cardiology Rebate Renewal</t>
+          <t>Corporate Access Renewal Defense</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
@@ -1005,68 +1156,85 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>OPP-4006</t>
+          <t>CUST-1006</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>Cityline Payer Alliance</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Contract Renewal</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>Payer / Managed Account</t>
+          <t>Direct Corporate Account</t>
         </is>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
+          <t>Region A</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
           <t>Priya Shah</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>Jordan Blake</t>
         </is>
       </c>
-      <c r="K10" s="13" t="inlineStr">
+      <c r="L10" s="13" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="L10" s="13" t="inlineStr">
+      <c r="M10" s="13" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="M10" s="13" t="inlineStr">
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="O10" s="13" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="P10" s="13" t="inlineStr">
         <is>
           <t>Net 90</t>
         </is>
       </c>
-      <c r="N10" s="13" t="n">
-        <v>48</v>
-      </c>
-      <c r="O10" s="13" t="inlineStr">
-        <is>
-          <t>Payer renewal for preferred formulary tier and cardiology volume.</t>
-        </is>
-      </c>
-      <c r="P10" s="13" t="inlineStr">
+      <c r="Q10" s="13" t="inlineStr">
+        <is>
+          <t>Contract renewal needed to defend incumbent position after competitor entry; proposed terms protect covered demand while recognizing access pressure.</t>
+        </is>
+      </c>
+      <c r="R10" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="Q10" s="13" t="inlineStr">
-        <is>
-          <t>Payer / Managed Account</t>
-        </is>
-      </c>
-      <c r="R10" s="13" t="inlineStr">
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Incumbent defense</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Direct Corporate Account</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1080,7 +1248,7 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Crescent Public Oncology Tender</t>
+          <t>Region C Public Tender Bid</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
@@ -1095,68 +1263,85 @@
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>OPP-4007</t>
+          <t>CUST-1009</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
+          <t>Crescent Public Tender Authority</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
           <t>Tender</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>LATAM</t>
-        </is>
-      </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>Public Procurement</t>
+          <t>Buying Group</t>
         </is>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
+          <t>Region C</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
           <t>Maya Chen</t>
         </is>
       </c>
-      <c r="J11" s="13" t="inlineStr">
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t>Jordan Blake</t>
         </is>
       </c>
-      <c r="K11" s="13" t="inlineStr">
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="L11" s="13" t="inlineStr">
+      <c r="M11" s="13" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="M11" s="13" t="inlineStr">
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>2027-04-30</t>
+        </is>
+      </c>
+      <c r="P11" s="13" t="inlineStr">
         <is>
           <t>Net 75</t>
         </is>
       </c>
-      <c r="N11" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="O11" s="13" t="inlineStr">
-        <is>
-          <t>Public tender defense for oncology and hospital injectable access.</t>
-        </is>
-      </c>
-      <c r="P11" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
       <c r="Q11" s="13" t="inlineStr">
         <is>
-          <t>Public Procurement</t>
+          <t>Public tender bid with price visibility risk requiring pricing governance review; discount aims to retain award eligibility without breaching margin floor.</t>
         </is>
       </c>
       <c r="R11" s="13" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Public tender</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Buying Group</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1170,83 +1355,100 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Atlas Hospital Diagnostic Framework</t>
+          <t>Institution Diagnostic Framework Launch</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
+          <t>CUST-1018</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Sterling Specialty Distribution</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
           <t>CUST-1013</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>Atlas Hospital Network</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>OPP-4008</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>New Sale</t>
-        </is>
-      </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>New Account / Launch</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>Hospital Network</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
+          <t>Region B</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
           <t>Sofia Romano</t>
         </is>
       </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>Lena Torres</t>
-        </is>
-      </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
+          <t>Jordan Blake</t>
+        </is>
+      </c>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="L12" s="13" t="inlineStr">
+      <c r="M12" s="13" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="M12" s="13" t="inlineStr">
+      <c r="N12" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="O12" s="13" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+      <c r="P12" s="13" t="inlineStr">
         <is>
           <t>Net 60</t>
         </is>
       </c>
-      <c r="N12" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="O12" s="13" t="inlineStr">
-        <is>
-          <t>Hospital framework for companion diagnostics and oncology oral therapy.</t>
-        </is>
-      </c>
-      <c r="P12" s="13" t="inlineStr">
+      <c r="Q12" s="13" t="inlineStr">
+        <is>
+          <t>Strategic launch support for institutional diagnostic framework; temporary discount secures protocol inclusion and expected recurring demand.</t>
+        </is>
+      </c>
+      <c r="R12" s="13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q12" s="13" t="inlineStr">
-        <is>
-          <t>Hospital Network</t>
-        </is>
-      </c>
-      <c r="R12" s="13" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>New account acquisition</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Distributor</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1260,7 +1462,7 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>BluePeak Immunology Access</t>
+          <t>Corporate Immunology Competitive Defense</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -1275,68 +1477,85 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>OPP-4009</t>
+          <t>CUST-1019</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>Strategic exception</t>
+          <t>BluePeak Payer Coalition</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Competitive Defense</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>Payer / Managed Account</t>
+          <t>Direct Corporate Account</t>
         </is>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
+          <t>Region A</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
           <t>Priya Shah</t>
         </is>
       </c>
-      <c r="J13" s="13" t="inlineStr">
+      <c r="K13" s="13" t="inlineStr">
         <is>
           <t>Jordan Blake</t>
         </is>
       </c>
-      <c r="K13" s="13" t="inlineStr">
+      <c r="L13" s="13" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="M13" s="13" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M13" s="13" t="inlineStr">
+      <c r="N13" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O13" s="13" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+      <c r="P13" s="13" t="inlineStr">
         <is>
           <t>Net 75</t>
         </is>
       </c>
-      <c r="N13" s="13" t="n">
-        <v>42</v>
-      </c>
-      <c r="O13" s="13" t="inlineStr">
-        <is>
-          <t>Payer coalition access for immunology biosimilars.</t>
-        </is>
-      </c>
-      <c r="P13" s="13" t="inlineStr">
+      <c r="Q13" s="13" t="inlineStr">
+        <is>
+          <t>Competitive defense against aggressive bidder pricing; requested discount protects annual volume while maintaining positive gross profit.</t>
+        </is>
+      </c>
+      <c r="R13" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="Q13" s="13" t="inlineStr">
-        <is>
-          <t>Payer / Managed Account</t>
-        </is>
-      </c>
-      <c r="R13" s="13" t="inlineStr">
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Competitor price pressure</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Direct Corporate Account</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1350,7 +1569,7 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>Metro Infusion Rare Disease Expansion</t>
+          <t>Institution Inventory Mitigation Offer</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -1365,68 +1584,85 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>OPP-4010</t>
+          <t>CUST-1020</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>Expansion</t>
+          <t>Metro Infusion Partners</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Inventory / Expiry Mitigation</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>Provider Network</t>
+          <t>Hospital / Institution</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
+          <t>Region A</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
           <t>Noah Patel</t>
         </is>
       </c>
-      <c r="J14" s="13" t="inlineStr">
-        <is>
-          <t>Lena Torres</t>
-        </is>
-      </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
+          <t>Jordan Blake</t>
+        </is>
+      </c>
+      <c r="L14" s="13" t="inlineStr">
+        <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="L14" s="13" t="inlineStr">
+      <c r="M14" s="13" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="M14" s="13" t="inlineStr">
+      <c r="N14" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="O14" s="13" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="P14" s="13" t="inlineStr">
         <is>
           <t>Net 45</t>
         </is>
       </c>
-      <c r="N14" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="O14" s="13" t="inlineStr">
-        <is>
-          <t>Infusion clinic rare disease expansion with patient access support.</t>
-        </is>
-      </c>
-      <c r="P14" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="Q14" s="13" t="inlineStr">
         <is>
-          <t>Provider Network</t>
+          <t>Inventory mitigation opportunity using near-expiry stock while preserving positive gross profit and supporting repeat demand.</t>
         </is>
       </c>
       <c r="R14" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Inventory / expiry mitigation</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Hospital / Institution</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1451,23 +1687,23 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="12.25" customWidth="1" min="1" max="1"/>
-    <col width="11.25" customWidth="1" min="2" max="2"/>
-    <col width="11.25" customWidth="1" min="3" max="3"/>
-    <col width="17.8799991607666" customWidth="1" min="4" max="4"/>
-    <col width="22.3799991607666" customWidth="1" min="5" max="5"/>
-    <col width="13.38000011444092" customWidth="1" min="6" max="6"/>
-    <col width="21.25" customWidth="1" min="7" max="7"/>
-    <col width="14.5" customWidth="1" min="8" max="8"/>
-    <col width="25.75" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="23.5" customWidth="1" min="11" max="11"/>
-    <col width="15.63000011444092" customWidth="1" min="12" max="12"/>
-    <col width="30.25" customWidth="1" min="13" max="13"/>
-    <col width="12.25" customWidth="1" min="14" max="14"/>
-    <col width="16.75" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="72" customWidth="1" min="15" max="15"/>
     <col width="14.5" customWidth="1" min="16" max="16"/>
     <col width="11.25" customWidth="1" min="17" max="17"/>
   </cols>
@@ -1475,101 +1711,91 @@
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Sample Deal Line Items</t>
+          <t>Sample Deal Line Items - Commercial Pricing Economics</t>
         </is>
       </c>
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Line-level product requests for all ten simulated deals.</t>
+          <t>Line-level commercial pricing requests with gross price, requested net price, revenue, cost, and rationale.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Deal ID</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Line #</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Product Name</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Therapeutic Area</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>Unit List Price</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Unit Gross Price</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Base Rebate %</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Requested Discount %</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>Requested Net Price</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>Proposed Unit Price</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>Extended List</t>
-        </is>
-      </c>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>Extended Proposed</t>
-        </is>
-      </c>
-      <c r="L4" s="11" t="inlineStr">
-        <is>
-          <t>Discount %</t>
-        </is>
-      </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>Gross Revenue</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>Proposed Net Revenue</t>
+        </is>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
         <is>
           <t>Requested Delivery Date</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
-      </c>
-      <c r="O4" s="11" t="inlineStr">
-        <is>
-          <t>Supply Risk</t>
-        </is>
-      </c>
-      <c r="P4" s="11" t="inlineStr">
-        <is>
-          <t>Line Type</t>
-        </is>
-      </c>
-      <c r="Q4" s="11" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
+          <t>Line Commercial Rationale</t>
         </is>
       </c>
     </row>
@@ -1589,58 +1815,44 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Oncavax IV 100mg Vial</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Oncology</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="n">
+          <t>Product Alpha</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n">
         <v>120</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="F5" s="16" t="n">
         <v>1850</v>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="G5" s="16" t="n">
+        <v>1776</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J5" s="16" t="n">
+        <v>1456.32</v>
+      </c>
+      <c r="K5" s="16" t="n">
         <v>555</v>
       </c>
-      <c r="I5" s="13" t="n">
-        <v>1517</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>222000</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>182040</v>
-      </c>
-      <c r="L5" s="13" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="M5" s="13" t="inlineStr">
+      <c r="L5" s="16" t="n">
+        <v>213120</v>
+      </c>
+      <c r="M5" s="16" t="n">
+        <v>174758.4</v>
+      </c>
+      <c r="N5" s="18" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="N5" s="13" t="inlineStr">
-        <is>
-          <t>Cold Chain 2-8C</t>
-        </is>
-      </c>
-      <c r="O5" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P5" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q5" s="13" t="inlineStr">
-        <is>
-          <t>Initial infusion network order</t>
+      <c r="O5" s="19" t="inlineStr">
+        <is>
+          <t>Discount requested to match expected competitor bid while preserving committed annual volume.</t>
         </is>
       </c>
     </row>
@@ -1660,58 +1872,44 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Oncavax IV 500mg Vial</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Oncology</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="n">
+          <t>Product Beta</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="F6" s="16" t="n">
         <v>7200</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="G6" s="16" t="n">
+        <v>6840</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J6" s="16" t="n">
+        <v>5608.8</v>
+      </c>
+      <c r="K6" s="16" t="n">
         <v>2160</v>
       </c>
-      <c r="I6" s="13" t="n">
-        <v>5904</v>
-      </c>
-      <c r="J6" s="13" t="n">
-        <v>288000</v>
-      </c>
-      <c r="K6" s="13" t="n">
-        <v>236160</v>
-      </c>
-      <c r="L6" s="13" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="M6" s="13" t="inlineStr">
+      <c r="L6" s="16" t="n">
+        <v>273600</v>
+      </c>
+      <c r="M6" s="16" t="n">
+        <v>224352</v>
+      </c>
+      <c r="N6" s="18" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="N6" s="13" t="inlineStr">
-        <is>
-          <t>Cold Chain 2-8C</t>
-        </is>
-      </c>
-      <c r="O6" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P6" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q6" s="13" t="inlineStr">
-        <is>
-          <t>High-value cold-chain line</t>
+      <c r="O6" s="19" t="inlineStr">
+        <is>
+          <t>Bundle line included to protect strategic volume and maintain continuity for high-value demand.</t>
         </is>
       </c>
     </row>
@@ -1731,58 +1929,44 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Rheumera Biosimilar Pen</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Immunology</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="n">
+          <t>Product Gamma</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n">
         <v>500</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="F7" s="16" t="n">
         <v>1180</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="G7" s="16" t="n">
+        <v>1121</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>986.48</v>
+      </c>
+      <c r="K7" s="16" t="n">
         <v>413</v>
       </c>
-      <c r="I7" s="13" t="n">
-        <v>1038.4</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>590000</v>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>519200</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M7" s="13" t="inlineStr">
+      <c r="L7" s="16" t="n">
+        <v>560500</v>
+      </c>
+      <c r="M7" s="16" t="n">
+        <v>493240</v>
+      </c>
+      <c r="N7" s="18" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="N7" s="13" t="inlineStr">
-        <is>
-          <t>Cold Chain 2-8C</t>
-        </is>
-      </c>
-      <c r="O7" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P7" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q7" s="13" t="inlineStr">
-        <is>
-          <t>Biosimilar conversion</t>
+      <c r="O7" s="19" t="inlineStr">
+        <is>
+          <t>Conversion discount supports account onboarding while preserving repeat-volume economics.</t>
         </is>
       </c>
     </row>
@@ -1802,58 +1986,44 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Companion Diagnostic Panel</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>Diagnostics</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="n">
+          <t>Product Zeta</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="n">
         <v>75</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="F8" s="16" t="n">
         <v>950</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="G8" s="16" t="n">
+        <v>902.5</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>794.2</v>
+      </c>
+      <c r="K8" s="16" t="n">
         <v>333</v>
       </c>
-      <c r="I8" s="13" t="n">
-        <v>836</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <v>71250</v>
-      </c>
-      <c r="K8" s="13" t="n">
-        <v>62700</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M8" s="13" t="inlineStr">
+      <c r="L8" s="16" t="n">
+        <v>67687.5</v>
+      </c>
+      <c r="M8" s="16" t="n">
+        <v>59565</v>
+      </c>
+      <c r="N8" s="18" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="N8" s="13" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="O8" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P8" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q8" s="13" t="inlineStr">
-        <is>
-          <t>Diagnostic support</t>
+      <c r="O8" s="19" t="inlineStr">
+        <is>
+          <t>Bundle line included to support account conversion and protect strategic volume.</t>
         </is>
       </c>
     </row>
@@ -1873,58 +2043,44 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Cardiovex 50mg Tablet Pack</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>Cardiology</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="n">
+          <t>Product Delta</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="F9" s="16" t="n">
         <v>420</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="G9" s="16" t="n">
+        <v>394.8</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J9" s="16" t="n">
+        <v>307.94</v>
+      </c>
+      <c r="K9" s="16" t="n">
         <v>147</v>
       </c>
-      <c r="I9" s="13" t="n">
-        <v>327.6</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>6300000</v>
-      </c>
-      <c r="K9" s="13" t="n">
-        <v>4914000</v>
-      </c>
-      <c r="L9" s="13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="M9" s="13" t="inlineStr">
+      <c r="L9" s="16" t="n">
+        <v>5922000</v>
+      </c>
+      <c r="M9" s="16" t="n">
+        <v>4619100</v>
+      </c>
+      <c r="N9" s="18" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="N9" s="13" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="O9" s="13" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P9" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q9" s="13" t="inlineStr">
-        <is>
-          <t>Preferred formulary volume</t>
+      <c r="O9" s="19" t="inlineStr">
+        <is>
+          <t>Higher discount requested for public tender; price visibility risk flagged for governance review.</t>
         </is>
       </c>
     </row>
@@ -1944,58 +2100,44 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Tumorex Oral 28-Day Pack</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>Oncology</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="n">
+          <t>Product Iota</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="n">
         <v>90</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="F10" s="16" t="n">
         <v>9400</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="G10" s="16" t="n">
+        <v>9024</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J10" s="16" t="n">
+        <v>7038.72</v>
+      </c>
+      <c r="K10" s="16" t="n">
         <v>2820</v>
       </c>
-      <c r="I10" s="13" t="n">
-        <v>7332</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>846000</v>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>659880</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="M10" s="13" t="inlineStr">
+      <c r="L10" s="16" t="n">
+        <v>812160</v>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>633484.8</v>
+      </c>
+      <c r="N10" s="18" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="N10" s="13" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="O10" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P10" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q10" s="13" t="inlineStr">
-        <is>
-          <t>Oncology oral access bundle</t>
+      <c r="O10" s="19" t="inlineStr">
+        <is>
+          <t>Access bundle supports broader award scope while keeping positive gross profit.</t>
         </is>
       </c>
     </row>
@@ -2015,58 +2157,44 @@
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Lysomab Rare Disease Kit</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>Rare Disease</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="n">
+          <t>Product Epsilon</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="F11" s="16" t="n">
         <v>28600</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="G11" s="16" t="n">
+        <v>27170</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J11" s="16" t="n">
+        <v>17932.2</v>
+      </c>
+      <c r="K11" s="16" t="n">
         <v>7150</v>
       </c>
-      <c r="I11" s="13" t="n">
-        <v>18876</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>572000</v>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>377520</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="M11" s="13" t="inlineStr">
+      <c r="L11" s="16" t="n">
+        <v>543400</v>
+      </c>
+      <c r="M11" s="16" t="n">
+        <v>358644</v>
+      </c>
+      <c r="N11" s="18" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="N11" s="13" t="inlineStr">
-        <is>
-          <t>Cold Chain 2-8C</t>
-        </is>
-      </c>
-      <c r="O11" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P11" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q11" s="13" t="inlineStr">
-        <is>
-          <t>EU rare disease allocation</t>
+      <c r="O11" s="19" t="inlineStr">
+        <is>
+          <t>Launch support discount requested to secure stocking commitment in a new regional account.</t>
         </is>
       </c>
     </row>
@@ -2086,58 +2214,44 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Nervomab Infusion Kit</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>Rare Disease</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="n">
+          <t>Product Kappa</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="F12" s="16" t="n">
         <v>34800</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="G12" s="16" t="n">
+        <v>33060</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J12" s="16" t="n">
+        <v>21819.6</v>
+      </c>
+      <c r="K12" s="16" t="n">
         <v>8700</v>
       </c>
-      <c r="I12" s="13" t="n">
-        <v>22968</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>348000</v>
-      </c>
-      <c r="K12" s="13" t="n">
-        <v>229680</v>
-      </c>
-      <c r="L12" s="13" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="M12" s="13" t="inlineStr">
+      <c r="L12" s="16" t="n">
+        <v>330600</v>
+      </c>
+      <c r="M12" s="16" t="n">
+        <v>218196</v>
+      </c>
+      <c r="N12" s="18" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="N12" s="13" t="inlineStr">
-        <is>
-          <t>Cold Chain 2-8C</t>
-        </is>
-      </c>
-      <c r="O12" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P12" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q12" s="13" t="inlineStr">
-        <is>
-          <t>Infusion kit launch support</t>
+      <c r="O12" s="19" t="inlineStr">
+        <is>
+          <t>Bundle line supports initial account conversion and repeat demand creation.</t>
         </is>
       </c>
     </row>
@@ -2157,58 +2271,44 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Rheumera Biosimilar Pen</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>Immunology</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="n">
+          <t>Product Gamma</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="n">
         <v>180</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="F13" s="16" t="n">
         <v>1180</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="G13" s="16" t="n">
+        <v>1121</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J13" s="16" t="n">
+        <v>1064.95</v>
+      </c>
+      <c r="K13" s="16" t="n">
         <v>413</v>
       </c>
-      <c r="I13" s="13" t="n">
-        <v>1121</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>212400</v>
-      </c>
-      <c r="K13" s="13" t="n">
+      <c r="L13" s="16" t="n">
         <v>201780</v>
       </c>
-      <c r="L13" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M13" s="13" t="inlineStr">
+      <c r="M13" s="16" t="n">
+        <v>191691</v>
+      </c>
+      <c r="N13" s="18" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="N13" s="13" t="inlineStr">
-        <is>
-          <t>Cold Chain 2-8C</t>
-        </is>
-      </c>
-      <c r="O13" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P13" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q13" s="13" t="inlineStr">
-        <is>
-          <t>Pilot conversion</t>
+      <c r="O13" s="19" t="inlineStr">
+        <is>
+          <t>Limited discount supports pilot conversion while staying within standard commercial guidance.</t>
         </is>
       </c>
     </row>
@@ -2228,58 +2328,44 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Companion Diagnostic Panel</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>Diagnostics</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="n">
+          <t>Product Zeta</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="F14" s="16" t="n">
         <v>950</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="G14" s="16" t="n">
+        <v>902.5</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J14" s="16" t="n">
+        <v>857.38</v>
+      </c>
+      <c r="K14" s="16" t="n">
         <v>333</v>
       </c>
-      <c r="I14" s="13" t="n">
-        <v>902.5</v>
-      </c>
-      <c r="J14" s="13" t="n">
-        <v>76000</v>
-      </c>
-      <c r="K14" s="13" t="n">
+      <c r="L14" s="16" t="n">
         <v>72200</v>
       </c>
-      <c r="L14" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M14" s="13" t="inlineStr">
+      <c r="M14" s="16" t="n">
+        <v>68590.39999999999</v>
+      </c>
+      <c r="N14" s="18" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="N14" s="13" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="O14" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P14" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q14" s="13" t="inlineStr">
-        <is>
-          <t>Companion diagnostics</t>
+      <c r="O14" s="19" t="inlineStr">
+        <is>
+          <t>Bundle line included to support account conversion and protect strategic volume.</t>
         </is>
       </c>
     </row>
@@ -2299,58 +2385,44 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Cardiovex 50mg Tablet Pack</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>Cardiology</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="n">
+          <t>Product Delta</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="n">
         <v>22000</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="F15" s="16" t="n">
         <v>420</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="G15" s="16" t="n">
+        <v>394.8</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J15" s="16" t="n">
+        <v>276.36</v>
+      </c>
+      <c r="K15" s="16" t="n">
         <v>147</v>
       </c>
-      <c r="I15" s="13" t="n">
-        <v>294</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>9240000</v>
-      </c>
-      <c r="K15" s="13" t="n">
-        <v>6468000</v>
-      </c>
-      <c r="L15" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M15" s="13" t="inlineStr">
+      <c r="L15" s="16" t="n">
+        <v>8685600</v>
+      </c>
+      <c r="M15" s="16" t="n">
+        <v>6079920</v>
+      </c>
+      <c r="N15" s="18" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="N15" s="13" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="O15" s="13" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P15" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q15" s="13" t="inlineStr">
-        <is>
-          <t>Payer renewal pressure</t>
+      <c r="O15" s="19" t="inlineStr">
+        <is>
+          <t>Contract renewal discount defends incumbent position after competitor entry.</t>
         </is>
       </c>
     </row>
@@ -2370,58 +2442,44 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Thrombex Hospital Pack</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>Cardiology</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="n">
+          <t>Product Eta</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="n">
         <v>900</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="F16" s="16" t="n">
         <v>1320</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="G16" s="16" t="n">
+        <v>1240.8</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J16" s="16" t="n">
+        <v>868.5599999999999</v>
+      </c>
+      <c r="K16" s="16" t="n">
         <v>462</v>
       </c>
-      <c r="I16" s="13" t="n">
-        <v>924</v>
-      </c>
-      <c r="J16" s="13" t="n">
-        <v>1188000</v>
-      </c>
-      <c r="K16" s="13" t="n">
-        <v>831600</v>
-      </c>
-      <c r="L16" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M16" s="13" t="inlineStr">
+      <c r="L16" s="16" t="n">
+        <v>1116720</v>
+      </c>
+      <c r="M16" s="16" t="n">
+        <v>781704</v>
+      </c>
+      <c r="N16" s="18" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="N16" s="13" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="O16" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P16" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q16" s="13" t="inlineStr">
-        <is>
-          <t>Hospital supply extension</t>
+      <c r="O16" s="19" t="inlineStr">
+        <is>
+          <t>Bundle line preserves institutional volume and protects renewal scope.</t>
         </is>
       </c>
     </row>
@@ -2441,58 +2499,44 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>Oncavax IV 100mg Vial</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>Oncology</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="n">
+          <t>Product Alpha</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="n">
         <v>600</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="F17" s="16" t="n">
         <v>1850</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="G17" s="16" t="n">
+        <v>1776</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J17" s="16" t="n">
+        <v>1278.72</v>
+      </c>
+      <c r="K17" s="16" t="n">
         <v>555</v>
       </c>
-      <c r="I17" s="13" t="n">
-        <v>1332</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>1110000</v>
-      </c>
-      <c r="K17" s="13" t="n">
-        <v>799200</v>
-      </c>
-      <c r="L17" s="13" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="M17" s="13" t="inlineStr">
+      <c r="L17" s="16" t="n">
+        <v>1065600</v>
+      </c>
+      <c r="M17" s="16" t="n">
+        <v>767232</v>
+      </c>
+      <c r="N17" s="18" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="N17" s="13" t="inlineStr">
-        <is>
-          <t>Cold Chain 2-8C</t>
-        </is>
-      </c>
-      <c r="O17" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P17" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q17" s="13" t="inlineStr">
-        <is>
-          <t>Tender vial supply</t>
+      <c r="O17" s="19" t="inlineStr">
+        <is>
+          <t>Higher discount requested for public tender; price visibility risk flagged.</t>
         </is>
       </c>
     </row>
@@ -2512,58 +2556,44 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>Thrombex Hospital Pack</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>Cardiology</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="n">
+          <t>Product Eta</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="n">
         <v>1200</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="F18" s="16" t="n">
         <v>1320</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="G18" s="16" t="n">
+        <v>1240.8</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J18" s="16" t="n">
+        <v>893.38</v>
+      </c>
+      <c r="K18" s="16" t="n">
         <v>462</v>
       </c>
-      <c r="I18" s="13" t="n">
-        <v>950.4</v>
-      </c>
-      <c r="J18" s="13" t="n">
-        <v>1584000</v>
-      </c>
-      <c r="K18" s="13" t="n">
-        <v>1140480</v>
-      </c>
-      <c r="L18" s="13" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="M18" s="13" t="inlineStr">
+      <c r="L18" s="16" t="n">
+        <v>1488960</v>
+      </c>
+      <c r="M18" s="16" t="n">
+        <v>1072056</v>
+      </c>
+      <c r="N18" s="18" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="N18" s="13" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="O18" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P18" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q18" s="13" t="inlineStr">
-        <is>
-          <t>Tender hospital pack</t>
+      <c r="O18" s="19" t="inlineStr">
+        <is>
+          <t>Tender support line included to protect award volume across the full package.</t>
         </is>
       </c>
     </row>
@@ -2583,58 +2613,44 @@
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>GeneMap Companion Panel</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>Diagnostics</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="n">
+          <t>Product Lambda</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="n">
         <v>250</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="F19" s="16" t="n">
         <v>1280</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="G19" s="16" t="n">
+        <v>1216</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J19" s="16" t="n">
+        <v>1021.44</v>
+      </c>
+      <c r="K19" s="16" t="n">
         <v>448</v>
       </c>
-      <c r="I19" s="13" t="n">
-        <v>1075.2</v>
-      </c>
-      <c r="J19" s="13" t="n">
-        <v>320000</v>
-      </c>
-      <c r="K19" s="13" t="n">
-        <v>268800</v>
-      </c>
-      <c r="L19" s="13" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="M19" s="13" t="inlineStr">
+      <c r="L19" s="16" t="n">
+        <v>304000</v>
+      </c>
+      <c r="M19" s="16" t="n">
+        <v>255360</v>
+      </c>
+      <c r="N19" s="18" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="N19" s="13" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="O19" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P19" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q19" s="13" t="inlineStr">
-        <is>
-          <t>Genomic companion diagnostics</t>
+      <c r="O19" s="19" t="inlineStr">
+        <is>
+          <t>Strategic launch support discount expected to secure framework listing and repeat demand.</t>
         </is>
       </c>
     </row>
@@ -2654,58 +2670,44 @@
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>Tumorex Oral 28-Day Pack</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>Oncology</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="n">
+          <t>Product Iota</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="n">
         <v>70</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="F20" s="16" t="n">
         <v>9400</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="G20" s="16" t="n">
+        <v>9024</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J20" s="16" t="n">
+        <v>7580.16</v>
+      </c>
+      <c r="K20" s="16" t="n">
         <v>2820</v>
       </c>
-      <c r="I20" s="13" t="n">
-        <v>7896</v>
-      </c>
-      <c r="J20" s="13" t="n">
-        <v>658000</v>
-      </c>
-      <c r="K20" s="13" t="n">
-        <v>552720</v>
-      </c>
-      <c r="L20" s="13" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="M20" s="13" t="inlineStr">
+      <c r="L20" s="16" t="n">
+        <v>631680</v>
+      </c>
+      <c r="M20" s="16" t="n">
+        <v>530611.2</v>
+      </c>
+      <c r="N20" s="18" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="N20" s="13" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-      <c r="O20" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P20" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q20" s="13" t="inlineStr">
-        <is>
-          <t>Oral oncology framework</t>
+      <c r="O20" s="19" t="inlineStr">
+        <is>
+          <t>Bundle line included to support account conversion and protect strategic volume.</t>
         </is>
       </c>
     </row>
@@ -2725,58 +2727,44 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>Dermava Biosimilar Syringe</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>Immunology</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="n">
+          <t>Product Theta</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="n">
         <v>850</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="F21" s="16" t="n">
         <v>980</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="G21" s="16" t="n">
+        <v>931</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J21" s="16" t="n">
+        <v>707.5599999999999</v>
+      </c>
+      <c r="K21" s="16" t="n">
         <v>343</v>
       </c>
-      <c r="I21" s="13" t="n">
-        <v>744.8</v>
-      </c>
-      <c r="J21" s="13" t="n">
-        <v>833000</v>
-      </c>
-      <c r="K21" s="13" t="n">
-        <v>633080</v>
-      </c>
-      <c r="L21" s="13" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="M21" s="13" t="inlineStr">
+      <c r="L21" s="16" t="n">
+        <v>791350</v>
+      </c>
+      <c r="M21" s="16" t="n">
+        <v>601426</v>
+      </c>
+      <c r="N21" s="18" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="N21" s="13" t="inlineStr">
-        <is>
-          <t>Cold Chain 2-8C</t>
-        </is>
-      </c>
-      <c r="O21" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P21" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q21" s="13" t="inlineStr">
-        <is>
-          <t>Dermatology biosimilar access</t>
+      <c r="O21" s="19" t="inlineStr">
+        <is>
+          <t>Discount requested to match expected competitor bid while preserving volume commitment.</t>
         </is>
       </c>
     </row>
@@ -2796,58 +2784,44 @@
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>Rheumera Biosimilar Pen</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>Immunology</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="n">
+          <t>Product Gamma</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="n">
         <v>700</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="F22" s="16" t="n">
         <v>1180</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="G22" s="16" t="n">
+        <v>1121</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J22" s="16" t="n">
+        <v>851.96</v>
+      </c>
+      <c r="K22" s="16" t="n">
         <v>413</v>
       </c>
-      <c r="I22" s="13" t="n">
-        <v>896.8</v>
-      </c>
-      <c r="J22" s="13" t="n">
-        <v>826000</v>
-      </c>
-      <c r="K22" s="13" t="n">
-        <v>627760</v>
-      </c>
-      <c r="L22" s="13" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="M22" s="13" t="inlineStr">
+      <c r="L22" s="16" t="n">
+        <v>784700</v>
+      </c>
+      <c r="M22" s="16" t="n">
+        <v>596372</v>
+      </c>
+      <c r="N22" s="18" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="N22" s="13" t="inlineStr">
-        <is>
-          <t>Cold Chain 2-8C</t>
-        </is>
-      </c>
-      <c r="O22" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P22" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q22" s="13" t="inlineStr">
-        <is>
-          <t>Rheumatology formulary access</t>
+      <c r="O22" s="19" t="inlineStr">
+        <is>
+          <t>Competitive defense line protects strategic volume in a multi-product access request.</t>
         </is>
       </c>
     </row>
@@ -2867,58 +2841,44 @@
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>Nervomab Infusion Kit</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>Rare Disease</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="n">
+          <t>Product Kappa</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="F23" s="16" t="n">
         <v>34800</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="G23" s="16" t="n">
+        <v>33060</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J23" s="16" t="n">
+        <v>21158.4</v>
+      </c>
+      <c r="K23" s="16" t="n">
         <v>8700</v>
       </c>
-      <c r="I23" s="13" t="n">
-        <v>22272</v>
-      </c>
-      <c r="J23" s="13" t="n">
-        <v>487200</v>
-      </c>
-      <c r="K23" s="13" t="n">
-        <v>311808</v>
-      </c>
-      <c r="L23" s="13" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M23" s="13" t="inlineStr">
+      <c r="L23" s="16" t="n">
+        <v>462840</v>
+      </c>
+      <c r="M23" s="16" t="n">
+        <v>296217.6</v>
+      </c>
+      <c r="N23" s="18" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="N23" s="13" t="inlineStr">
-        <is>
-          <t>Cold Chain 2-8C</t>
-        </is>
-      </c>
-      <c r="O23" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P23" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q23" s="13" t="inlineStr">
-        <is>
-          <t>Rare disease infusion expansion</t>
+      <c r="O23" s="19" t="inlineStr">
+        <is>
+          <t>Near-expiry allocation proposed to avoid write-off while maintaining positive gross profit.</t>
         </is>
       </c>
     </row>
@@ -2938,62 +2898,49 @@
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>Lysomab Rare Disease Kit</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>Rare Disease</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="n">
+          <t>Product Epsilon</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="F24" s="16" t="n">
         <v>28600</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="G24" s="16" t="n">
+        <v>27170</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J24" s="16" t="n">
+        <v>17388.8</v>
+      </c>
+      <c r="K24" s="16" t="n">
         <v>7150</v>
       </c>
-      <c r="I24" s="13" t="n">
-        <v>18304</v>
-      </c>
-      <c r="J24" s="13" t="n">
-        <v>343200</v>
-      </c>
-      <c r="K24" s="13" t="n">
-        <v>219648</v>
-      </c>
-      <c r="L24" s="13" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M24" s="13" t="inlineStr">
+      <c r="L24" s="16" t="n">
+        <v>326040</v>
+      </c>
+      <c r="M24" s="16" t="n">
+        <v>208665.6</v>
+      </c>
+      <c r="N24" s="18" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="N24" s="13" t="inlineStr">
-        <is>
-          <t>Cold Chain 2-8C</t>
-        </is>
-      </c>
-      <c r="O24" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P24" s="13" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="Q24" s="13" t="inlineStr">
-        <is>
-          <t>Rare disease kit expansion</t>
+      <c r="O24" s="19" t="inlineStr">
+        <is>
+          <t>Inventory mitigation discount supports uptake of aging stock while preserving contribution.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:O24"/>
   <mergeCells count="2">
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
@@ -3011,90 +2958,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="12.25" customWidth="1" min="1" max="1"/>
-    <col width="15.63000011444092" customWidth="1" min="2" max="2"/>
-    <col width="13.38000011444092" customWidth="1" min="3" max="3"/>
-    <col width="15.63000011444092" customWidth="1" min="4" max="4"/>
-    <col width="20.1299991607666" customWidth="1" min="5" max="5"/>
-    <col width="21.25" customWidth="1" min="6" max="6"/>
-    <col width="15.63000011444092" customWidth="1" min="7" max="7"/>
-    <col width="16.75" customWidth="1" min="8" max="8"/>
-    <col width="20.1299991607666" customWidth="1" min="9" max="9"/>
-    <col width="11.25" customWidth="1" min="10" max="10"/>
-    <col width="31.25" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="56" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Deal Summary</t>
+          <t>Deal Summary - Executive Approval Summary</t>
         </is>
       </c>
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Deal-level calculated summary with financial plan inclusion flag.</t>
+          <t>Calculated from Deal Header and Line Items; risk score, route, and recommendation use transparent approval rules.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Deal ID</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Deal Title</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Total List</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Total Proposed</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Sold-To Customer</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>End Account</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Gross Revenue</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Proposed Net Revenue</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>Discount Amount</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>Intake Risk</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>Expected Route</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>Gross Margin %</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>KAM Risk Assessment</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>Risk Reason</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>System Risk Score</t>
+        </is>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>Approval Route</t>
+        </is>
+      </c>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
+          <t>Business Recommendation</t>
+        </is>
+      </c>
+      <c r="P4" s="14" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>Included_In_Latest_Financial_Plan</t>
+      <c r="Q4" s="14" t="inlineStr">
+        <is>
+          <t>Included In Latest Financial Plan</t>
         </is>
       </c>
     </row>
@@ -3106,42 +3089,72 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Northstar Oncology Infusion Expansion</t>
+          <t>Region A Infusion Tender Defense</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
+          <t>HelioRx Distribution</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
           <t>Northstar Health Systems</t>
         </is>
       </c>
-      <c r="D5" s="13" t="n">
-        <v>510000</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>418200</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>91800</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="E5" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A5,'Line Items'!$L$5:$L$24)</f>
+        <v/>
+      </c>
+      <c r="F5" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A5,'Line Items'!$M$5:$M$24)</f>
+        <v/>
+      </c>
+      <c r="G5" s="16">
+        <f>E5-F5</f>
+        <v/>
+      </c>
+      <c r="H5" s="17">
+        <f>IF(E5=0,0,G5/E5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="16">
+        <f>F5-SUMPRODUCT(('Line Items'!$A$5:$A$24=A5)*'Line Items'!$E$5:$E$24*'Line Items'!$K$5:$K$24)</f>
+        <v/>
+      </c>
+      <c r="J5" s="17">
+        <f>IF(F5=0,0,I5/F5)</f>
+        <v/>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>See approval route</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>Competitor price pressure</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>Sales Manager → Pricing Governance Owner → Market Access Director → Finance Director → General Manager</t>
+        </is>
+      </c>
+      <c r="O5" s="20" t="inlineStr">
+        <is>
+          <t>Escalate to General Manager</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3155,7 +3168,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Meridian Biosimilar Conversion</t>
+          <t>Retail Chain Conversion Program</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -3163,34 +3176,64 @@
           <t>Meridian Specialty Pharmacy</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
-        <v>661250</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <v>532525</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>128725</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>0.1946691871455576</v>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Meridian Specialty Pharmacy</t>
+        </is>
+      </c>
+      <c r="E6" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A6,'Line Items'!$L$5:$L$24)</f>
+        <v/>
+      </c>
+      <c r="F6" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A6,'Line Items'!$M$5:$M$24)</f>
+        <v/>
+      </c>
+      <c r="G6" s="16">
+        <f>E6-F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="17">
+        <f>IF(E6=0,0,G6/E6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="16">
+        <f>F6-SUMPRODUCT(('Line Items'!$A$5:$A$24=A6)*'Line Items'!$E$5:$E$24*'Line Items'!$K$5:$K$24)</f>
+        <v/>
+      </c>
+      <c r="J6" s="17">
+        <f>IF(F6=0,0,I6/F6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>See approval route</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>New account acquisition</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>Sales Manager → Pricing Governance Owner → Market Access Director → Finance Director → Supply Chain Manager</t>
+        </is>
+      </c>
+      <c r="O6" s="20" t="inlineStr">
+        <is>
+          <t>Request Revision</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="K6" s="13" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3204,7 +3247,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Apex National Formulary Access</t>
+          <t>National Buying Group Renewal</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
@@ -3212,34 +3255,64 @@
           <t>Apex National GPO</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
-        <v>7146000</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>5622000</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>1524000</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>0.2132661628883291</v>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Apex National GPO</t>
+        </is>
+      </c>
+      <c r="E7" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A7,'Line Items'!$L$5:$L$24)</f>
+        <v/>
+      </c>
+      <c r="F7" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A7,'Line Items'!$M$5:$M$24)</f>
+        <v/>
+      </c>
+      <c r="G7" s="16">
+        <f>E7-F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="17">
+        <f>IF(E7=0,0,G7/E7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="16">
+        <f>F7-SUMPRODUCT(('Line Items'!$A$5:$A$24=A7)*'Line Items'!$E$5:$E$24*'Line Items'!$K$5:$K$24)</f>
+        <v/>
+      </c>
+      <c r="J7" s="17">
+        <f>IF(F7=0,0,I7/F7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>See approval route</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>Incumbent defense</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" s="20" t="inlineStr">
+        <is>
+          <t>Sales Manager → Pricing Governance Owner → Market Access Director → Finance Director → Supply Chain Manager → General Manager</t>
+        </is>
+      </c>
+      <c r="O7" s="20" t="inlineStr">
+        <is>
+          <t>Escalate to General Manager</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3253,7 +3326,7 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>HelioRx Rare Disease EU Launch</t>
+          <t>Region B Launch Stocking Offer</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -3261,34 +3334,64 @@
           <t>HelioRx Distribution</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
-        <v>920000</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <v>740600</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>179400</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>See approval route</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Orion Hospital Trust</t>
+        </is>
+      </c>
+      <c r="E8" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A8,'Line Items'!$L$5:$L$24)</f>
+        <v/>
+      </c>
+      <c r="F8" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A8,'Line Items'!$M$5:$M$24)</f>
+        <v/>
+      </c>
+      <c r="G8" s="16">
+        <f>E8-F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="17">
+        <f>IF(E8=0,0,G8/E8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="16">
+        <f>F8-SUMPRODUCT(('Line Items'!$A$5:$A$24=A8)*'Line Items'!$E$5:$E$24*'Line Items'!$K$5:$K$24)</f>
+        <v/>
+      </c>
+      <c r="J8" s="17">
+        <f>IF(F8=0,0,I8/F8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>New account acquisition</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="20" t="inlineStr">
+        <is>
+          <t>Sales Manager → Pricing Governance Owner → Market Access Director → Finance Director → General Manager</t>
+        </is>
+      </c>
+      <c r="O8" s="20" t="inlineStr">
+        <is>
+          <t>Reject - Below Margin Floor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="K8" s="13" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3302,7 +3405,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Summit Oncology Biosimilar Pilot</t>
+          <t>Institution Pilot Access Package</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -3310,34 +3413,64 @@
           <t>Summit Oncology Clinics</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
-        <v>288400</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>245100</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>43300</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0.1501386962552011</v>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Summit Oncology Clinics</t>
+        </is>
+      </c>
+      <c r="E9" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A9,'Line Items'!$L$5:$L$24)</f>
+        <v/>
+      </c>
+      <c r="F9" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A9,'Line Items'!$M$5:$M$24)</f>
+        <v/>
+      </c>
+      <c r="G9" s="16">
+        <f>E9-F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="17">
+        <f>IF(E9=0,0,G9/E9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="16">
+        <f>F9-SUMPRODUCT(('Line Items'!$A$5:$A$24=A9)*'Line Items'!$E$5:$E$24*'Line Items'!$K$5:$K$24)</f>
+        <v/>
+      </c>
+      <c r="J9" s="17">
+        <f>IF(F9=0,0,I9/F9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>See approval route</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>New account acquisition</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="20" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="K9" s="13" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3351,7 +3484,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>Cityline Cardiology Rebate Renewal</t>
+          <t>Corporate Access Renewal Defense</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
@@ -3359,34 +3492,64 @@
           <t>Cityline Payer Alliance</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n">
-        <v>10428000</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>7471000</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>2957000</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>0.2835634829305715</v>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Cityline Payer Alliance</t>
+        </is>
+      </c>
+      <c r="E10" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A10,'Line Items'!$L$5:$L$24)</f>
+        <v/>
+      </c>
+      <c r="F10" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A10,'Line Items'!$M$5:$M$24)</f>
+        <v/>
+      </c>
+      <c r="G10" s="16">
+        <f>E10-F10</f>
+        <v/>
+      </c>
+      <c r="H10" s="17">
+        <f>IF(E10=0,0,G10/E10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="16">
+        <f>F10-SUMPRODUCT(('Line Items'!$A$5:$A$24=A10)*'Line Items'!$E$5:$E$24*'Line Items'!$K$5:$K$24)</f>
+        <v/>
+      </c>
+      <c r="J10" s="17">
+        <f>IF(F10=0,0,I10/F10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>See approval route</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>Incumbent defense</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>Sales Manager → Pricing Governance Owner → Market Access Director → Finance Director → Supply Chain Manager → General Manager</t>
+        </is>
+      </c>
+      <c r="O10" s="20" t="inlineStr">
+        <is>
+          <t>Reject - Below Margin Floor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="K10" s="13" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3400,7 +3563,7 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Crescent Public Oncology Tender</t>
+          <t>Region C Public Tender Bid</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
@@ -3408,34 +3571,64 @@
           <t>Crescent Public Tender Authority</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
-        <v>2694000</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>2121000</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>573000</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>0.2126948775055679</v>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>See approval route</t>
-        </is>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Crescent Public Tender Authority</t>
+        </is>
+      </c>
+      <c r="E11" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A11,'Line Items'!$L$5:$L$24)</f>
+        <v/>
+      </c>
+      <c r="F11" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A11,'Line Items'!$M$5:$M$24)</f>
+        <v/>
+      </c>
+      <c r="G11" s="16">
+        <f>E11-F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="17">
+        <f>IF(E11=0,0,G11/E11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="16">
+        <f>F11-SUMPRODUCT(('Line Items'!$A$5:$A$24=A11)*'Line Items'!$E$5:$E$24*'Line Items'!$K$5:$K$24)</f>
+        <v/>
+      </c>
+      <c r="J11" s="17">
+        <f>IF(F11=0,0,I11/F11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>Public tender</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>Sales Manager → Pricing Governance Owner → Market Access Director → Finance Director → Supply Chain Manager → General Manager</t>
+        </is>
+      </c>
+      <c r="O11" s="20" t="inlineStr">
+        <is>
+          <t>Reject - Below Margin Floor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="K11" s="13" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3449,42 +3642,72 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Atlas Hospital Diagnostic Framework</t>
+          <t>Institution Diagnostic Framework Launch</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
+          <t>Sterling Specialty Distribution</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
           <t>Atlas Hospital Network</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
-        <v>978000</v>
-      </c>
-      <c r="E12" s="13" t="n">
-        <v>803500</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>174500</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>0.1784253578732106</v>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
+      <c r="E12" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A12,'Line Items'!$L$5:$L$24)</f>
+        <v/>
+      </c>
+      <c r="F12" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A12,'Line Items'!$M$5:$M$24)</f>
+        <v/>
+      </c>
+      <c r="G12" s="16">
+        <f>E12-F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="17">
+        <f>IF(E12=0,0,G12/E12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="16">
+        <f>F12-SUMPRODUCT(('Line Items'!$A$5:$A$24=A12)*'Line Items'!$E$5:$E$24*'Line Items'!$K$5:$K$24)</f>
+        <v/>
+      </c>
+      <c r="J12" s="17">
+        <f>IF(F12=0,0,I12/F12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>See approval route</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>New account acquisition</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>Sales Manager → Pricing Governance Owner → Market Access Director → Finance Director → General Manager</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr">
+        <is>
+          <t>Request Revision</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="K12" s="13" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3498,7 +3721,7 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>BluePeak Immunology Access</t>
+          <t>Corporate Immunology Competitive Defense</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -3506,34 +3729,64 @@
           <t>BluePeak Payer Coalition</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
-        <v>1659000</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>1314250</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>344750</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0.2078059071729958</v>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>BluePeak Payer Coalition</t>
+        </is>
+      </c>
+      <c r="E13" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A13,'Line Items'!$L$5:$L$24)</f>
+        <v/>
+      </c>
+      <c r="F13" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A13,'Line Items'!$M$5:$M$24)</f>
+        <v/>
+      </c>
+      <c r="G13" s="16">
+        <f>E13-F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="17">
+        <f>IF(E13=0,0,G13/E13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="16">
+        <f>F13-SUMPRODUCT(('Line Items'!$A$5:$A$24=A13)*'Line Items'!$E$5:$E$24*'Line Items'!$K$5:$K$24)</f>
+        <v/>
+      </c>
+      <c r="J13" s="17">
+        <f>IF(F13=0,0,I13/F13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>See approval route</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>Competitor price pressure</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
+        <is>
+          <t>Sales Manager → Pricing Governance Owner → Market Access Director → Finance Director → Supply Chain Manager → General Manager</t>
+        </is>
+      </c>
+      <c r="O13" s="20" t="inlineStr">
+        <is>
+          <t>Escalate to General Manager</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="K13" s="13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3547,7 +3800,7 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>Metro Infusion Rare Disease Expansion</t>
+          <t>Institution Inventory Mitigation Offer</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -3555,40 +3808,71 @@
           <t>Metro Infusion Partners</t>
         </is>
       </c>
-      <c r="D14" s="13" t="n">
-        <v>830400</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <v>680600</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>149800</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <v>0.1803949903660886</v>
-      </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>See approval route</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Metro Infusion Partners</t>
+        </is>
+      </c>
+      <c r="E14" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A14,'Line Items'!$L$5:$L$24)</f>
+        <v/>
+      </c>
+      <c r="F14" s="16">
+        <f>SUMIF('Line Items'!$A$5:$A$24,A14,'Line Items'!$M$5:$M$24)</f>
+        <v/>
+      </c>
+      <c r="G14" s="16">
+        <f>E14-F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="17">
+        <f>IF(E14=0,0,G14/E14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="16">
+        <f>F14-SUMPRODUCT(('Line Items'!$A$5:$A$24=A14)*'Line Items'!$E$5:$E$24*'Line Items'!$K$5:$K$24)</f>
+        <v/>
+      </c>
+      <c r="J14" s="17">
+        <f>IF(F14=0,0,I14/F14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>Inventory / expiry mitigation</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
+        <is>
+          <t>Sales Manager → Pricing Governance Owner → Market Access Director → Finance Director → General Manager</t>
+        </is>
+      </c>
+      <c r="O14" s="20" t="inlineStr">
+        <is>
+          <t>Reject - Below Margin Floor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Submitted</t>
         </is>
       </c>
-      <c r="K14" s="13" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:Q14"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>

--- a/demo-data/Sample_Deal_Requests.xlsx
+++ b/demo-data/Sample_Deal_Requests.xlsx
@@ -13,12 +13,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="168" formatCode="$#,##0"/>
+    <numFmt numFmtId="167" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -109,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -157,7 +156,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -236,7 +238,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SampleDeals" displayName="SampleDeals" ref="A4:U7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SampleDeals" displayName="SampleDeals" ref="A4:AC10" headerRowCount="1">
   <autoFilter ref="A4:U14"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Deal ID"/>
@@ -266,7 +268,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SampleLineItems" displayName="SampleLineItems" ref="A4:O7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SampleLineItems" displayName="SampleLineItems" ref="A4:O10" headerRowCount="1">
   <autoFilter ref="A4:O24"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Deal ID"/>
@@ -290,7 +292,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DealSummary" displayName="DealSummary" ref="A4:Q7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DealSummary" displayName="DealSummary" ref="A4:Q10" headerRowCount="1">
   <autoFilter ref="A4:Q14"/>
   <tableColumns count="17">
     <tableColumn id="1" name="Deal ID"/>
@@ -466,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.25" customWidth="1" min="1" max="1"/>
@@ -609,6 +611,46 @@
           <t>Included In Latest Financial Plan</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Last Decision</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Last Decision Comment</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Last Decision Timestamp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Last Decision Actor</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Last Decision Role</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Last Approval Step</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Previous Status</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Returned For Changes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -668,7 +710,7 @@
       </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Changes Requested</t>
         </is>
       </c>
       <c r="M5" s="18" t="n">
@@ -687,7 +729,7 @@
       </c>
       <c r="Q5" s="13" t="inlineStr">
         <is>
-          <t>Tender defense against aggressive competitor pricing at Northstar Health Systems. The requested discount protects annual Product Alpha volume through HelioRx Distribution while staying within product guidance and preserving positive gross profit.</t>
+          <t>Tender defense against aggressive competitor pricing at Northstar Health Systems. The requested Product Alpha discount protects annual volume through HelioRx Distribution, but the revision needs clearer volume upside and spillover controls before first-line approval.</t>
         </is>
       </c>
       <c r="R5" s="13" t="inlineStr">
@@ -709,6 +751,44 @@
         <is>
           <t>Yes</t>
         </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Request Changes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Please quantify expected volume gain after the requested discount and add supporting competitor pricing evidence.</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:20:00</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Jordan Blake</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="AC5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -719,7 +799,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Apex GPO Contract Renewal - Product Delta</t>
+          <t>Apex National Buying Group Renewal - Product Delta</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -769,7 +849,7 @@
       </c>
       <c r="L6" s="13" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="M6" s="18" t="n">
@@ -788,7 +868,7 @@
       </c>
       <c r="Q6" s="13" t="inlineStr">
         <is>
-          <t>Contract renewal required to defend the incumbent Product Delta position at Apex National GPO after competitor entry. The proposal balances access retention, volume continuity and margin discipline for a strategic buying group.</t>
+          <t>National buying group renewal for Product Delta after competitor entry. The requested discount protects incumbent formulary position and planned volume while recognizing Apex National GPO credit watch status.</t>
         </is>
       </c>
       <c r="R6" s="13" t="inlineStr">
@@ -810,6 +890,9 @@
         <is>
           <t>Yes</t>
         </is>
+      </c>
+      <c r="AC6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -820,27 +903,27 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Meridian Competitive Pressure - Product Gamma</t>
+          <t>BluePeak Competitive Pricing Response - Product Theta</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>CUST-1002</t>
+          <t>CUST-1019</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Meridian Specialty Pharmacy</t>
+          <t>BluePeak Payer Coalition</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>CUST-1002</t>
+          <t>CUST-1019</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Meridian Specialty Pharmacy</t>
+          <t>BluePeak Payer Coalition</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
@@ -850,128 +933,488 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>Retail / Pharmacy Chain</t>
+          <t>Direct Corporate Account</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
+          <t>Region A</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>Maya Chen</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>Jordan Blake</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="M7" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="N7" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O7" s="18" t="n">
+        <v>46568</v>
+      </c>
+      <c r="P7" s="13" t="inlineStr">
+        <is>
+          <t>Net 75</t>
+        </is>
+      </c>
+      <c r="Q7" s="13" t="inlineStr">
+        <is>
+          <t>Competitive pricing response for Product Theta after a rival access offer to BluePeak Payer Coalition. The case has passed first-line commercial review and now needs parallel commercial governance and finance review.</t>
+        </is>
+      </c>
+      <c r="R7" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Competitor price pressure</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Direct Corporate Account</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Commercial rationale is directionally sound. Please proceed to governance and finance review for discount and margin validation.</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:05:00</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Jordan Blake</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="AC7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>DEAL-4004</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Orion Hospital Contract Renewal - Product Eta</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>CUST-1007</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Orion Hospital Trust</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>CUST-1007</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Orion Hospital Trust</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Contract Renewal</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>Hospital / Institution</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
           <t>Region B</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>Ethan Brooks</t>
         </is>
       </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="K8" s="13" t="inlineStr">
         <is>
           <t>Jordan Blake</t>
         </is>
       </c>
-      <c r="L7" s="13" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="M7" s="18" t="n">
-        <v>46249</v>
-      </c>
-      <c r="N7" s="18" t="n">
-        <v>46254</v>
-      </c>
-      <c r="O7" s="18" t="n">
-        <v>46356</v>
-      </c>
-      <c r="P7" s="13" t="inlineStr">
-        <is>
-          <t>Net 45</t>
-        </is>
-      </c>
-      <c r="Q7" s="13" t="inlineStr">
-        <is>
-          <t>Competitive price pressure on Product Gamma at Meridian Specialty Pharmacy. The draft request evaluates whether a focused discount can protect expected retail-chain volume while maintaining acceptable contribution.</t>
-        </is>
-      </c>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>Changes Requested</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="n">
+        <v>46264</v>
+      </c>
+      <c r="N8" s="18" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O8" s="18" t="n">
+        <v>46418</v>
+      </c>
+      <c r="P8" s="13" t="inlineStr">
+        <is>
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="Q8" s="13" t="inlineStr">
+        <is>
+          <t>Hospital contract renewal for Product Eta at Orion Hospital Trust. The account is strategically relevant in Region B, but credit hold and incomplete forecast assumptions require revision before approval can proceed.</t>
+        </is>
+      </c>
+      <c r="R8" s="13" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Budget constraints</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Hospital / Institution</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Request Changes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Budget impact should include updated forecast assumptions and the spillover risk assessment is incomplete.</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2026-06-24 15:10:00</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Jordan Blake</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="AC8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>DEAL-4005</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Atlas New Account Access - Product Gamma</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>CUST-1013</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Atlas Hospital Network</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>CUST-1013</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Atlas Hospital Network</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>New Account / Launch</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>Hospital / Institution</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>Region B</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>Ethan Brooks</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>Jordan Blake</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="M9" s="18" t="n">
+        <v>46295</v>
+      </c>
+      <c r="N9" s="18" t="n">
+        <v>46305</v>
+      </c>
+      <c r="O9" s="18" t="n">
+        <v>46446</v>
+      </c>
+      <c r="P9" s="13" t="inlineStr">
+        <is>
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="Q9" s="13" t="inlineStr">
+        <is>
+          <t>New account access proposal for Product Gamma at Atlas Hospital Network. Short-term discount is expected to secure listing, build protocol familiarity and unlock repeat institutional demand.</t>
+        </is>
+      </c>
+      <c r="R9" s="13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Competitor price pressure</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Retail / Pharmacy Chain</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>New account acquisition</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Hospital / Institution</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>DEAL-4006</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Sterling Distributor Negotiation - Product Zeta</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>CUST-1018</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Sterling Specialty Distribution</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>CUST-1013</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Atlas Hospital Network</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Strategic Opportunity</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>Distributor</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>Region B</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>Ethan Brooks</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Jordan Blake</t>
+        </is>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="M10" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="N10" s="18" t="n">
+        <v>46327</v>
+      </c>
+      <c r="O10" s="18" t="n">
+        <v>46507</v>
+      </c>
+      <c r="P10" s="13" t="inlineStr">
+        <is>
+          <t>Net 60</t>
+        </is>
+      </c>
+      <c r="Q10" s="13" t="inlineStr">
+        <is>
+          <t>Distributor negotiation for Product Zeta through Sterling Specialty Distribution to support Atlas Hospital Network access. Sales Manager has approved the commercial logic; parallel governance and finance review are pending.</t>
+        </is>
+      </c>
+      <c r="R10" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Volume commitment requirement</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Distributor</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="n"/>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="13" t="n"/>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="n"/>
-      <c r="M8" s="13" t="n"/>
-      <c r="N8" s="13" t="n"/>
-      <c r="O8" s="13" t="n"/>
-      <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="13" t="n"/>
-      <c r="R8" s="13" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="n"/>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="13" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="13" t="n"/>
-      <c r="L9" s="13" t="n"/>
-      <c r="M9" s="13" t="n"/>
-      <c r="N9" s="13" t="n"/>
-      <c r="O9" s="13" t="n"/>
-      <c r="P9" s="13" t="n"/>
-      <c r="Q9" s="13" t="n"/>
-      <c r="R9" s="13" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="n"/>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="13" t="n"/>
-      <c r="L10" s="13" t="n"/>
-      <c r="M10" s="13" t="n"/>
-      <c r="N10" s="13" t="n"/>
-      <c r="O10" s="13" t="n"/>
-      <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="13" t="n"/>
-      <c r="R10" s="13" t="n"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Distributor volume commitment is credible. Proceed to governance and finance validation of discount and plan impact.</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:35:00</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Jordan Blake</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="AC10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="n"/>
@@ -1204,12 +1647,12 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="F5" s="21" t="n">
+        <v>65</v>
+      </c>
+      <c r="F5" s="22" t="n">
         <v>1850</v>
       </c>
-      <c r="G5" s="21" t="n">
+      <c r="G5" s="22" t="n">
         <v>1776</v>
       </c>
       <c r="H5" s="17" t="n">
@@ -1218,24 +1661,24 @@
       <c r="I5" s="17" t="n">
         <v>0.18</v>
       </c>
-      <c r="J5" s="21" t="n">
+      <c r="J5" s="22" t="n">
         <v>1456.32</v>
       </c>
-      <c r="K5" s="21" t="n">
+      <c r="K5" s="22" t="n">
         <v>555</v>
       </c>
-      <c r="L5" s="21" t="n">
-        <v>213120</v>
-      </c>
-      <c r="M5" s="21" t="n">
-        <v>174758.4</v>
+      <c r="L5" s="22" t="n">
+        <v>115440</v>
+      </c>
+      <c r="M5" s="22" t="n">
+        <v>94660.8</v>
       </c>
       <c r="N5" s="18" t="n">
         <v>46249</v>
       </c>
       <c r="O5" s="19" t="inlineStr">
         <is>
-          <t>Discount requested to match expected competitor tender bid while preserving the committed annual Product Alpha volume.</t>
+          <t>Tender defense discount requested to match expected competitor bid while preserving Northstar annual volume commitment.</t>
         </is>
       </c>
     </row>
@@ -1259,38 +1702,38 @@
         </is>
       </c>
       <c r="E6" s="15" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F6" s="21" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F6" s="22" t="n">
         <v>420</v>
       </c>
-      <c r="G6" s="21" t="n">
+      <c r="G6" s="22" t="n">
         <v>394.8</v>
       </c>
       <c r="H6" s="17" t="n">
         <v>0.06</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J6" s="21" t="n">
-        <v>307.94</v>
-      </c>
-      <c r="K6" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J6" s="22" t="n">
+        <v>355.32</v>
+      </c>
+      <c r="K6" s="22" t="n">
         <v>147</v>
       </c>
-      <c r="L6" s="21" t="n">
-        <v>5922000</v>
-      </c>
-      <c r="M6" s="21" t="n">
-        <v>4619100</v>
+      <c r="L6" s="22" t="n">
+        <v>3553200</v>
+      </c>
+      <c r="M6" s="22" t="n">
+        <v>3197880</v>
       </c>
       <c r="N6" s="18" t="n">
         <v>46280</v>
       </c>
       <c r="O6" s="19" t="inlineStr">
         <is>
-          <t>Renewal discount defends incumbent Product Delta position after competitor entry while preserving positive gross profit.</t>
+          <t>Renewal discount protects national buying group volume while staying within a controlled governance tier.</t>
         </is>
       </c>
     </row>
@@ -1305,22 +1748,22 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>BIO-RA-200</t>
+          <t>BIO-DERM-80</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Product Gamma</t>
+          <t>Product Theta</t>
         </is>
       </c>
       <c r="E7" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="F7" s="21" t="n">
-        <v>1180</v>
-      </c>
-      <c r="G7" s="21" t="n">
-        <v>1121</v>
+        <v>180</v>
+      </c>
+      <c r="F7" s="22" t="n">
+        <v>980</v>
+      </c>
+      <c r="G7" s="22" t="n">
+        <v>931</v>
       </c>
       <c r="H7" s="17" t="n">
         <v>0.05</v>
@@ -1328,77 +1771,191 @@
       <c r="I7" s="17" t="n">
         <v>0.12</v>
       </c>
-      <c r="J7" s="21" t="n">
-        <v>986.48</v>
-      </c>
-      <c r="K7" s="21" t="n">
+      <c r="J7" s="22" t="n">
+        <v>819.28</v>
+      </c>
+      <c r="K7" s="22" t="n">
+        <v>343</v>
+      </c>
+      <c r="L7" s="22" t="n">
+        <v>167580</v>
+      </c>
+      <c r="M7" s="22" t="n">
+        <v>147470.4</v>
+      </c>
+      <c r="N7" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="O7" s="19" t="inlineStr">
+        <is>
+          <t>Discount requested to neutralize competitor pricing while protecting strategic managed account volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>DEAL-4004</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>RX-HOSP-20</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Product Eta</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>1320</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>1240.8</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>1067.09</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>462</v>
+      </c>
+      <c r="L8" s="22" t="n">
+        <v>620400</v>
+      </c>
+      <c r="M8" s="22" t="n">
+        <v>533545</v>
+      </c>
+      <c r="N8" s="18" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O8" s="19" t="inlineStr">
+        <is>
+          <t>Renewal discount protects hospital continuity, but forecast assumptions and credit implications require clarification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>DEAL-4005</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>BIO-RA-200</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Product Gamma</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>350</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <v>1180</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>1121</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J9" s="22" t="n">
+        <v>1031.32</v>
+      </c>
+      <c r="K9" s="22" t="n">
         <v>413</v>
       </c>
-      <c r="L7" s="21" t="n">
-        <v>560500</v>
-      </c>
-      <c r="M7" s="21" t="n">
-        <v>493240</v>
-      </c>
-      <c r="N7" s="18" t="n">
-        <v>46254</v>
-      </c>
-      <c r="O7" s="19" t="inlineStr">
-        <is>
-          <t>Draft discount scenario responds to competitive price pressure while preserving repeat-volume economics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="n"/>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="16" t="n"/>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="17" t="n"/>
-      <c r="I8" s="17" t="n"/>
-      <c r="J8" s="16" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="16" t="n"/>
-      <c r="M8" s="16" t="n"/>
-      <c r="N8" s="18" t="n"/>
-      <c r="O8" s="19" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="n"/>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="17" t="n"/>
-      <c r="I9" s="17" t="n"/>
-      <c r="J9" s="16" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="16" t="n"/>
-      <c r="M9" s="16" t="n"/>
-      <c r="N9" s="18" t="n"/>
-      <c r="O9" s="19" t="n"/>
+      <c r="L9" s="22" t="n">
+        <v>392350</v>
+      </c>
+      <c r="M9" s="22" t="n">
+        <v>360962</v>
+      </c>
+      <c r="N9" s="18" t="n">
+        <v>46305</v>
+      </c>
+      <c r="O9" s="19" t="inlineStr">
+        <is>
+          <t>Launch discount supports account conversion and future repeat demand while preserving contribution.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n"/>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="17" t="n"/>
-      <c r="I10" s="17" t="n"/>
-      <c r="J10" s="16" t="n"/>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="16" t="n"/>
-      <c r="M10" s="16" t="n"/>
-      <c r="N10" s="18" t="n"/>
-      <c r="O10" s="19" t="n"/>
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>DEAL-4006</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>DX-COMP-01</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Product Zeta</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>200</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>950</v>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>902.5</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J10" s="22" t="n">
+        <v>794.2</v>
+      </c>
+      <c r="K10" s="22" t="n">
+        <v>333</v>
+      </c>
+      <c r="L10" s="22" t="n">
+        <v>180500</v>
+      </c>
+      <c r="M10" s="22" t="n">
+        <v>158840</v>
+      </c>
+      <c r="N10" s="18" t="n">
+        <v>46327</v>
+      </c>
+      <c r="O10" s="19" t="inlineStr">
+        <is>
+          <t>Distributor discount supports committed conversion volume without creating a public price precedent.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="n"/>
@@ -1800,20 +2357,20 @@
           <t>Northstar Health Systems</t>
         </is>
       </c>
-      <c r="E5" s="21" t="n">
-        <v>213120</v>
-      </c>
-      <c r="F5" s="21" t="n">
-        <v>174758.4</v>
-      </c>
-      <c r="G5" s="21" t="n">
-        <v>38361.60000000001</v>
+      <c r="E5" s="22" t="n">
+        <v>115440</v>
+      </c>
+      <c r="F5" s="22" t="n">
+        <v>94660.8</v>
+      </c>
+      <c r="G5" s="22" t="n">
+        <v>20779.2</v>
       </c>
       <c r="H5" s="17" t="n">
         <v>0.18</v>
       </c>
-      <c r="I5" s="21" t="n">
-        <v>108158.4</v>
+      <c r="I5" s="22" t="n">
+        <v>58585.8</v>
       </c>
       <c r="J5" s="17" t="n">
         <v>0.6189024390243902</v>
@@ -1833,17 +2390,17 @@
       </c>
       <c r="N5" s="20" t="inlineStr">
         <is>
-          <t>Sales Manager -&gt; Commercial Manager -&gt; Finance Manager</t>
+          <t>Submitted -&gt; Returned for Changes</t>
         </is>
       </c>
       <c r="O5" s="20" t="inlineStr">
         <is>
-          <t>Approve with Commercial Manager Review</t>
+          <t>Request Revision</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Changes Requested</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1860,7 +2417,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Apex GPO Contract Renewal - Product Delta</t>
+          <t>Apex National Buying Group Renewal - Product Delta</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -1873,23 +2430,23 @@
           <t>Apex National GPO</t>
         </is>
       </c>
-      <c r="E6" s="21" t="n">
-        <v>5922000</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>4619100</v>
-      </c>
-      <c r="G6" s="21" t="n">
-        <v>1302900</v>
+      <c r="E6" s="22" t="n">
+        <v>3553200</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>3197880</v>
+      </c>
+      <c r="G6" s="22" t="n">
+        <v>355320</v>
       </c>
       <c r="H6" s="17" t="n">
-        <v>0.2200101317122594</v>
-      </c>
-      <c r="I6" s="21" t="n">
-        <v>2414100</v>
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="22" t="n">
+        <v>1874880</v>
       </c>
       <c r="J6" s="17" t="n">
-        <v>0.5226342794050789</v>
+        <v>0.5862884160756501</v>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -1911,12 +2468,12 @@
       </c>
       <c r="O6" s="20" t="inlineStr">
         <is>
-          <t>Escalate to General Manager</t>
+          <t>Approve with Commercial Manager Review</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1933,118 +2490,289 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Meridian Competitive Pressure - Product Gamma</t>
+          <t>BluePeak Competitive Pricing Response - Product Theta</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Meridian Specialty Pharmacy</t>
+          <t>BluePeak Payer Coalition</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Meridian Specialty Pharmacy</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="n">
-        <v>560500</v>
-      </c>
-      <c r="F7" s="21" t="n">
-        <v>493240</v>
-      </c>
-      <c r="G7" s="21" t="n">
-        <v>67260</v>
+          <t>BluePeak Payer Coalition</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="n">
+        <v>167580</v>
+      </c>
+      <c r="F7" s="22" t="n">
+        <v>147470.4</v>
+      </c>
+      <c r="G7" s="22" t="n">
+        <v>20109.60000000001</v>
       </c>
       <c r="H7" s="17" t="n">
         <v>0.12</v>
       </c>
-      <c r="I7" s="21" t="n">
-        <v>286740</v>
+      <c r="I7" s="22" t="n">
+        <v>85730.39999999999</v>
       </c>
       <c r="J7" s="17" t="n">
         <v>0.5813397129186603</v>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>Competitor price pressure</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" s="20" t="inlineStr">
+        <is>
+          <t>Sales Manager -&gt; Commercial Manager -&gt; Finance Manager -&gt; General Manager</t>
+        </is>
+      </c>
+      <c r="O7" s="20" t="inlineStr">
+        <is>
+          <t>Approve with Commercial Manager Review</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>DEAL-4004</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Orion Hospital Contract Renewal - Product Eta</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Orion Hospital Trust</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Orion Hospital Trust</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>620400</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>533545</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>86855</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>0.139998388136686</v>
+      </c>
+      <c r="I8" s="22" t="n">
+        <v>302545</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>0.5670468282900224</v>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>Budget constraints</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" s="20" t="inlineStr">
+        <is>
+          <t>Submitted -&gt; Returned for Changes</t>
+        </is>
+      </c>
+      <c r="O8" s="20" t="inlineStr">
+        <is>
+          <t>Request Revision</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Changes Requested</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>DEAL-4005</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Atlas New Account Access - Product Gamma</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Atlas Hospital Network</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Atlas Hospital Network</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="n">
+        <v>392350</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <v>360962</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>31388</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I9" s="22" t="n">
+        <v>216412</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>0.5995423340961098</v>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="L7" s="20" t="inlineStr">
-        <is>
-          <t>Competitor price pressure</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>New account acquisition</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" s="20" t="inlineStr">
+        <is>
+          <t>Sales Manager -&gt; Commercial Manager -&gt; Finance Manager -&gt; General Manager</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr">
+        <is>
+          <t>Approve with Commercial Manager Review</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>DEAL-4006</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Sterling Distributor Negotiation - Product Zeta</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Sterling Specialty Distribution</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Atlas Hospital Network</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="n">
+        <v>180500</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>158840</v>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>21660</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I10" s="22" t="n">
+        <v>92240</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>0.5807101485771846</v>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>Volume commitment requirement</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
         <v>4</v>
       </c>
-      <c r="N7" s="20" t="inlineStr">
-        <is>
-          <t>Draft - not submitted</t>
-        </is>
-      </c>
-      <c r="O7" s="20" t="inlineStr">
-        <is>
-          <t>Draft - review before submission</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>Sales Manager -&gt; Commercial Manager -&gt; Finance Manager -&gt; General Manager</t>
+        </is>
+      </c>
+      <c r="O10" s="20" t="inlineStr">
+        <is>
+          <t>Approve with Commercial Manager Review</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="n"/>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="17" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="17" t="n"/>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="20" t="n"/>
-      <c r="N8" s="20" t="n"/>
-      <c r="O8" s="20" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="n"/>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="17" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="17" t="n"/>
-      <c r="K9" s="13" t="n"/>
-      <c r="L9" s="20" t="n"/>
-      <c r="N9" s="20" t="n"/>
-      <c r="O9" s="20" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="n"/>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="17" t="n"/>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="17" t="n"/>
-      <c r="K10" s="13" t="n"/>
-      <c r="L10" s="20" t="n"/>
-      <c r="N10" s="20" t="n"/>
-      <c r="O10" s="20" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="13" t="n"/>

--- a/demo-data/Sample_Deal_Requests.xlsx
+++ b/demo-data/Sample_Deal_Requests.xlsx
@@ -238,7 +238,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SampleDeals" displayName="SampleDeals" ref="A4:AC10" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SampleDeals" displayName="SampleDeals" ref="A4:AC14" headerRowCount="1">
   <autoFilter ref="A4:U14"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Deal ID"/>
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SampleLineItems" displayName="SampleLineItems" ref="A4:O10" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SampleLineItems" displayName="SampleLineItems" ref="A4:O24" headerRowCount="1">
   <autoFilter ref="A4:O24"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Deal ID"/>
@@ -292,7 +292,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DealSummary" displayName="DealSummary" ref="A4:Q10" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DealSummary" displayName="DealSummary" ref="A4:Q14" headerRowCount="1">
   <autoFilter ref="A4:Q14"/>
   <tableColumns count="17">
     <tableColumn id="1" name="Deal ID"/>
@@ -849,7 +849,7 @@
       </c>
       <c r="L6" s="13" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="M6" s="18" t="n">
@@ -953,7 +953,7 @@
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="M7" s="18" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="M9" s="18" t="n">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="M10" s="18" t="n">
@@ -1354,17 +1354,17 @@
       </c>
       <c r="Q10" s="13" t="inlineStr">
         <is>
-          <t>Distributor negotiation for Product Zeta through Sterling Specialty Distribution to support Atlas Hospital Network access. Sales Manager has approved the commercial logic; parallel governance and finance review are pending.</t>
+          <t>Distributor negotiation to protect regional access and defend committed volume. Requested pricing remains margin-positive, but available inventory is below the requested quantity in the priority warehouse and requires Operations confirmation before final commitment.</t>
         </is>
       </c>
       <c r="R10" s="13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Volume commitment requirement</t>
+          <t>Product Zeta request exceeds currently available inventory in the priority warehouse; allocation risk requires Operations review.</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="E6" s="15" t="n">
-        <v>9000</v>
+        <v>240</v>
       </c>
       <c r="F6" s="22" t="n">
         <v>420</v>
@@ -1723,17 +1723,17 @@
         <v>147</v>
       </c>
       <c r="L6" s="22" t="n">
-        <v>3553200</v>
+        <v>94752</v>
       </c>
       <c r="M6" s="22" t="n">
-        <v>3197880</v>
+        <v>85276.8</v>
       </c>
       <c r="N6" s="18" t="n">
         <v>46280</v>
       </c>
       <c r="O6" s="19" t="inlineStr">
         <is>
-          <t>Renewal discount protects national buying group volume while staying within a controlled governance tier.</t>
+          <t>Renewal volume reflects a focused national buying group commitment. Requested discount defends incumbent share without creating an inventory allocation issue.</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="E8" s="15" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="F8" s="22" t="n">
         <v>1320</v>
@@ -1833,17 +1833,17 @@
         <v>462</v>
       </c>
       <c r="L8" s="22" t="n">
-        <v>620400</v>
+        <v>223344</v>
       </c>
       <c r="M8" s="22" t="n">
-        <v>533545</v>
+        <v>192076.2</v>
       </c>
       <c r="N8" s="18" t="n">
         <v>46275</v>
       </c>
       <c r="O8" s="19" t="inlineStr">
         <is>
-          <t>Renewal discount protects hospital continuity, but forecast assumptions and credit implications require clarification.</t>
+          <t>Contract renewal request protects hospital continuity while keeping requested volume within current supply availability.</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="E9" s="15" t="n">
-        <v>350</v>
+        <v>220</v>
       </c>
       <c r="F9" s="22" t="n">
         <v>1180</v>
@@ -1888,17 +1888,17 @@
         <v>413</v>
       </c>
       <c r="L9" s="22" t="n">
-        <v>392350</v>
+        <v>246620</v>
       </c>
       <c r="M9" s="22" t="n">
-        <v>360962</v>
+        <v>226890.4</v>
       </c>
       <c r="N9" s="18" t="n">
         <v>46305</v>
       </c>
       <c r="O9" s="19" t="inlineStr">
         <is>
-          <t>Launch discount supports account conversion and future repeat demand while preserving contribution.</t>
+          <t>Launch-access discount supports listing conversion for a new account while keeping requested volume within available supply.</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="E10" s="15" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F10" s="22" t="n">
         <v>950</v>
@@ -1943,17 +1943,17 @@
         <v>333</v>
       </c>
       <c r="L10" s="22" t="n">
-        <v>180500</v>
+        <v>270750</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>158840</v>
+        <v>238260</v>
       </c>
       <c r="N10" s="18" t="n">
         <v>46327</v>
       </c>
       <c r="O10" s="19" t="inlineStr">
         <is>
-          <t>Distributor discount supports committed conversion volume without creating a public price precedent.</t>
+          <t>Distributor negotiation requires volume-backed price support, but current Product Zeta coverage is below two months in the priority warehouse, requiring controlled allocation review before commitment.</t>
         </is>
       </c>
     </row>
@@ -2431,22 +2431,22 @@
         </is>
       </c>
       <c r="E6" s="22" t="n">
-        <v>3553200</v>
+        <v>94752</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>3197880</v>
+        <v>85276.8</v>
       </c>
       <c r="G6" s="22" t="n">
-        <v>355320</v>
+        <v>9475.199999999997</v>
       </c>
       <c r="H6" s="17" t="n">
-        <v>0.1</v>
+        <v>0.09999999999999996</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>1874880</v>
+        <v>49996.8</v>
       </c>
       <c r="J6" s="17" t="n">
-        <v>0.5862884160756501</v>
+        <v>0.5862884160756502</v>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -2468,12 +2468,12 @@
       </c>
       <c r="O6" s="20" t="inlineStr">
         <is>
-          <t>Approve with Commercial Manager Review</t>
+          <t>Approve with Commercial and Finance Review</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -2577,19 +2577,19 @@
         </is>
       </c>
       <c r="E8" s="22" t="n">
-        <v>620400</v>
+        <v>223344</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>533545</v>
+        <v>192076.2</v>
       </c>
       <c r="G8" s="22" t="n">
-        <v>86855</v>
+        <v>31267.80000000002</v>
       </c>
       <c r="H8" s="17" t="n">
-        <v>0.139998388136686</v>
+        <v>0.1399983881366861</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>302545</v>
+        <v>108916.2</v>
       </c>
       <c r="J8" s="17" t="n">
         <v>0.5670468282900224</v>
@@ -2650,19 +2650,19 @@
         </is>
       </c>
       <c r="E9" s="22" t="n">
-        <v>392350</v>
+        <v>246620</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>360962</v>
+        <v>226890.4</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>31388</v>
+        <v>19729.60000000001</v>
       </c>
       <c r="H9" s="17" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000003</v>
       </c>
       <c r="I9" s="22" t="n">
-        <v>216412</v>
+        <v>136030.4</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>0.5995423340961098</v>
@@ -2687,12 +2687,12 @@
       </c>
       <c r="O9" s="20" t="inlineStr">
         <is>
-          <t>Approve with Commercial Manager Review</t>
+          <t>Approve with Commercial and Finance Review</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -2723,19 +2723,19 @@
         </is>
       </c>
       <c r="E10" s="22" t="n">
-        <v>180500</v>
+        <v>270750</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>158840</v>
+        <v>238260</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>21660</v>
+        <v>32490</v>
       </c>
       <c r="H10" s="17" t="n">
         <v>0.12</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>92240</v>
+        <v>138360</v>
       </c>
       <c r="J10" s="17" t="n">
         <v>0.5807101485771846</v>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N10" s="20" t="inlineStr">
         <is>
-          <t>Sales Manager -&gt; Commercial Manager -&gt; Finance Manager -&gt; General Manager</t>
+          <t>Sales Manager -&gt; Commercial Manager -&gt; Finance Manager -&gt; Operations Manager -&gt; General Manager</t>
         </is>
       </c>
       <c r="O10" s="20" t="inlineStr">
         <is>
-          <t>Approve with Commercial Manager Review</t>
+          <t>Approve with Finance, Commercial, and Operations Review</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">

--- a/demo-data/Sample_Deal_Requests.xlsx
+++ b/demo-data/Sample_Deal_Requests.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal Requests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Line Items" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Deal Requests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Line Items" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Deal Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -685,7 +685,7 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>Tender Bid</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="P7" s="13" t="inlineStr">
         <is>
-          <t>Net 75</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="Q7" s="13" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>New Account / Launch</t>
+          <t>New Account Launch</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Product Zeta request exceeds currently available inventory in the priority warehouse; allocation risk requires Operations review.</t>
+          <t>Inventory / expiry mitigation</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
